--- a/shucle_report/동면/20260330_20260405/report_동면_20260330_20260405.xlsx
+++ b/shucle_report/동면/20260330_20260405/report_동면_20260330_20260405.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-08 15:25 | 차트: 101개</t>
+          <t>분석기간: 2026.03.30 ~ 04.05 | 비교기간: 2026.03.23 ~ 03.29 | 생성: 2026-04-13 12:23 | 차트: 152개</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.6건</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.2건</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.6명</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -1404,32 +1404,32 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>피크 시간대 이동시간</t>
+          <t>피크 시간대(16~18시) 이동시간</t>
         </is>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-1.8</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>9.5→7.7분 감소</t>
         </is>
       </c>
     </row>
@@ -1441,32 +1441,32 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>비피크 시간대 이동시간</t>
+          <t>비피크 시간대(8~10시) 이동시간</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+3.0</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>+29.6%</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>10.3→13.3분 증가</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
     <row r="6">
       <c r="A6" s="11" t="inlineStr">
         <is>
-          <t>• 대기시간 안정: 3.7분 → 3.4분 (-9.9%) — 큰 변동 없음</t>
+          <t>• 호출당 평균 탑승객 1.8명: 동승 이용 활발</t>
         </is>
       </c>
     </row>
@@ -2616,7 +2616,7 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2771,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.6</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>데이터 없음</t>
+          <t>비교기간 데이터 없음</t>
         </is>
       </c>
     </row>
